--- a/tests/Tableau des tests.xlsx
+++ b/tests/Tableau des tests.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emman\Formation\P10_DSML\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5353A3D7-2CA5-40ED-821F-0DCC385AA16C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14F79A94-2043-4C42-8570-EDB72DA34FC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{8DA27DCD-3A9C-40B5-AEEB-35EEF2B41E1C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{8DA27DCD-3A9C-40B5-AEEB-35EEF2B41E1C}"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet name="Tests Ragas" sheetId="1" r:id="rId1"/>
+    <sheet name="Base" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="142">
   <si>
     <t>Catégorie</t>
   </si>
@@ -141,9 +142,6 @@
     <t>Les statistiques des Orlando Magic vont-elles dans le sens des critiques exprimées par les fans ?</t>
   </si>
   <si>
-    <t>Les statistiques ne vont pas dans le même sens que les bonnes critiques des fans car le nombre de points total de l'équipe des Orlando Magic est inférieur à la moyenne des équipes.</t>
-  </si>
-  <si>
     <t>ResponseRelevancy</t>
   </si>
   <si>
@@ -196,17 +194,314 @@
     <t>Le contexte fourni ne permet pas de répondre à cette question.
 Les données disponibles indiquent le nombre de victoires par joueur (`W`) ou des totaux de points, mais elles ne précisent pas quelles équipes ont remporté des matchs spécifiques ni les résultats globaux des équipes pour la saison en cours.</t>
   </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t>q</t>
+  </si>
+  <si>
+    <t>Player</t>
+  </si>
+  <si>
+    <t>Nom du joueur</t>
+  </si>
+  <si>
+    <t>Team</t>
+  </si>
+  <si>
+    <t>Équipe du joueur (code à 3 lettres)</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Âge du joueur</t>
+  </si>
+  <si>
+    <t>GP</t>
+  </si>
+  <si>
+    <t>Nombre de matchs joués (Games Played)</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>Nombre de victoires de l'équipe lors des matchs joués</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>Nombre de défaites</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>Minutes moyennes jouées par match</t>
+  </si>
+  <si>
+    <t>PTS</t>
+  </si>
+  <si>
+    <t>Points marqués en moyenne par match</t>
+  </si>
+  <si>
+    <t>FGM</t>
+  </si>
+  <si>
+    <t>Tirs réussis par match (Field Goals Made)</t>
+  </si>
+  <si>
+    <t>FGA</t>
+  </si>
+  <si>
+    <t>Tirs tentés par match (Field Goals Attempted)</t>
+  </si>
+  <si>
+    <t>FG%</t>
+  </si>
+  <si>
+    <t>Pourcentage de réussite aux tirs</t>
+  </si>
+  <si>
+    <t>Minutes jouées après 15:00 de jeu</t>
+  </si>
+  <si>
+    <t>3PA</t>
+  </si>
+  <si>
+    <t>Tirs à 3 points tentés par match</t>
+  </si>
+  <si>
+    <t>3P%</t>
+  </si>
+  <si>
+    <t>Pourcentage de réussite à 3 points</t>
+  </si>
+  <si>
+    <t>FTM</t>
+  </si>
+  <si>
+    <t>Lancers francs réussis (Free Throws Made)</t>
+  </si>
+  <si>
+    <t>FTA</t>
+  </si>
+  <si>
+    <t>Lancers francs tentés</t>
+  </si>
+  <si>
+    <t>FT%</t>
+  </si>
+  <si>
+    <t>Pourcentage de réussite aux lancers francs</t>
+  </si>
+  <si>
+    <t>OREB</t>
+  </si>
+  <si>
+    <t>Rebonds offensifs</t>
+  </si>
+  <si>
+    <t>DREB</t>
+  </si>
+  <si>
+    <t>Rebonds défensifs</t>
+  </si>
+  <si>
+    <t>REB</t>
+  </si>
+  <si>
+    <t>Rebonds totaux</t>
+  </si>
+  <si>
+    <t>AST</t>
+  </si>
+  <si>
+    <t>Passes décisives (Assists)</t>
+  </si>
+  <si>
+    <t>TOV</t>
+  </si>
+  <si>
+    <t>Balles perdues (Turnovers)</t>
+  </si>
+  <si>
+    <t>STL</t>
+  </si>
+  <si>
+    <t>Interceptions (Steals)</t>
+  </si>
+  <si>
+    <t>BLK</t>
+  </si>
+  <si>
+    <t>Contres (Blocks)</t>
+  </si>
+  <si>
+    <t>PF</t>
+  </si>
+  <si>
+    <t>Fautes personnelles</t>
+  </si>
+  <si>
+    <t>FP</t>
+  </si>
+  <si>
+    <t>Fantasy Points</t>
+  </si>
+  <si>
+    <t>DD2</t>
+  </si>
+  <si>
+    <t>Double-doubles (≥10 dans deux catégories principales)</t>
+  </si>
+  <si>
+    <t>TD3</t>
+  </si>
+  <si>
+    <t>Triple-doubles (≥10 dans trois catégories principales)</t>
+  </si>
+  <si>
+    <t>Plus-Minus (écart de score lorsque le joueur est sur le terrain)</t>
+  </si>
+  <si>
+    <t>OFFRTG</t>
+  </si>
+  <si>
+    <t>Offensive Rating (points marqués par 100 possessions)</t>
+  </si>
+  <si>
+    <t>DEFRTG</t>
+  </si>
+  <si>
+    <t>Defensive Rating (points encaissés par 100 possessions)</t>
+  </si>
+  <si>
+    <t>NETRTG</t>
+  </si>
+  <si>
+    <t>Net Rating = OFFRTG - DEFRTG</t>
+  </si>
+  <si>
+    <t>AST%</t>
+  </si>
+  <si>
+    <t>Pourcentage d'assists – implication dans les passes décisives</t>
+  </si>
+  <si>
+    <t>AST/TO</t>
+  </si>
+  <si>
+    <t>Ratio passes / pertes de balle</t>
+  </si>
+  <si>
+    <t>AST RATIO</t>
+  </si>
+  <si>
+    <t>Ratio d’assists pour 100 possessions</t>
+  </si>
+  <si>
+    <t>OREB%</t>
+  </si>
+  <si>
+    <t>Pourcentage de rebonds offensifs parmi ceux disponibles</t>
+  </si>
+  <si>
+    <t>DREB%</t>
+  </si>
+  <si>
+    <t>Idem en défensif</t>
+  </si>
+  <si>
+    <t>REB%</t>
+  </si>
+  <si>
+    <t>Pourcentage de rebonds totaux parmi ceux disponibles</t>
+  </si>
+  <si>
+    <t>TO RATIO</t>
+  </si>
+  <si>
+    <t>Turnover Ratio – pertes de balle par 100 possessions</t>
+  </si>
+  <si>
+    <t>EFG%</t>
+  </si>
+  <si>
+    <t>Effective Field Goal % (pondère les 3 points)</t>
+  </si>
+  <si>
+    <t>TS%</t>
+  </si>
+  <si>
+    <t>True Shooting % (inclut FG et FT dans l'efficacité)</t>
+  </si>
+  <si>
+    <t>USG%</t>
+  </si>
+  <si>
+    <t>Usage Rate – % des actions utilisées par le joueur</t>
+  </si>
+  <si>
+    <t>PACE</t>
+  </si>
+  <si>
+    <t>Rythme de jeu (possessions par 48 minutes)</t>
+  </si>
+  <si>
+    <t>PIE</t>
+  </si>
+  <si>
+    <t>Player Impact Estimate – évaluation globale de l’impact</t>
+  </si>
+  <si>
+    <t>POSS</t>
+  </si>
+  <si>
+    <t>Nombre total de possessions jouées</t>
+  </si>
+  <si>
+    <t>Table</t>
+  </si>
+  <si>
+    <t>players</t>
+  </si>
+  <si>
+    <t>matches</t>
+  </si>
+  <si>
+    <t>stats</t>
+  </si>
+  <si>
+    <t>reports</t>
+  </si>
+  <si>
+    <t>Column name</t>
+  </si>
+  <si>
+    <t>Label</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -218,7 +513,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -226,17 +521,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -580,13 +894,13 @@
         <v>2</v>
       </c>
       <c r="F1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" t="s">
         <v>34</v>
-      </c>
-      <c r="G1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -612,7 +926,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -638,7 +952,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -664,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="216" x14ac:dyDescent="0.3">
@@ -690,7 +1004,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -716,7 +1030,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -743,7 +1057,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
@@ -769,7 +1083,7 @@
         <v>0.92</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="144" x14ac:dyDescent="0.3">
@@ -795,7 +1109,7 @@
         <v>0.93</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
@@ -812,16 +1126,16 @@
         <v>31</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F10">
-        <v>0.78</v>
-      </c>
-      <c r="G10">
-        <v>0.87</v>
+        <v>21</v>
+      </c>
+      <c r="F10" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10" t="s">
+        <v>46</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -847,7 +1161,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
@@ -878,6 +1192,481 @@
     <row r="21" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{868031F0-F241-47AE-84C5-B3A2B0F88B3A}">
+  <dimension ref="A1:E46"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="49.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" t="s">
+        <v>137</v>
+      </c>
+      <c r="E5" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="4">
+        <v>0.625</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C18" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C19" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C22" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C25" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C26" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C27" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="str">
+        <f>"+ / -"</f>
+        <v>+ / -</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
